--- a/九龙-何文田-名钻/名钻_销控明细表.xlsx
+++ b/九龙-何文田-名钻/名钻_销控明细表.xlsx
@@ -982,7 +982,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2024-12-22</t>
+          <t>2024-12-23</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2025-01-08</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2024-12-22</t>
+          <t>2024-12-23</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2025-01-23</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2025-01-05</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2024-12-23</t>
+          <t>2024-12-24</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2024-09-25</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5878,7 +5878,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -6010,7 +6010,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -6218,7 +6218,7 @@
           <t>A | 821呎 (3房)
 $2132万
 $25,967/呎
-(26年-04月-28日)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -6226,7 +6226,7 @@
           <t>B | 533呎 (2房)
 $1849万
 $34,694/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -6234,7 +6234,7 @@
           <t>C | 819呎 (3房)
 $2488万
 $30,379/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -6242,7 +6242,7 @@
           <t>D | 423呎 (2房)
 $1065万
 $25,173/呎
-(26年-02月-26日)</t>
+(26年-02月-27日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -6250,7 +6250,7 @@
           <t>E | 448呎 (2房)
 $1196万
 $26,708/呎
-(25年-12月-21日)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -6273,7 +6273,7 @@
           <t>A | 821呎 (3房)
 $2060万
 $25,090/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -6281,7 +6281,7 @@
           <t>B | 533呎 (2房)
 $1458万
 $27,345/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -6289,7 +6289,7 @@
           <t>C | 819呎 (3房)
 $2065万
 $25,210/呎
-(25年-06月-10日)</t>
+(25年-06月-11日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -6297,7 +6297,7 @@
           <t>D | 423呎 (2房)
 $1025万
 $24,222/呎
-(25年-11月-06日)</t>
+(25年-11月-07日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -6305,7 +6305,7 @@
           <t>E | 448呎 (2房)
 $1477万
 $32,967/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="G7" s="23" t="inlineStr">
@@ -6328,7 +6328,7 @@
           <t>A | 821呎 (3房)
 $1987万
 $24,201/呎
-(25年-12月-10日)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -6336,7 +6336,7 @@
           <t>B | 533呎 (2房)
 $1407万
 $26,392/呎
-(26年-02月-25日)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -6344,7 +6344,7 @@
           <t>C | 819呎 (3房)
 $1992万
 $24,326/呎
-(25年-01月-15日)</t>
+(25年-01月-16日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -6352,7 +6352,7 @@
           <t>D | 423呎 (2房)
 $994万
 $23,499/呎
-(24年-12月-03日)</t>
+(24年-12月-04日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -6360,7 +6360,7 @@
           <t>E | 448呎 (2房)
 $1112万
 $24,819/呎
-(26年-01月-15日)</t>
+(26年-01月-16日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -6383,7 +6383,7 @@
           <t>A | 821呎 (3房)
 $1887万
 $22,981/呎
-(25年-03月-03日)</t>
+(25年-03月-04日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -6391,7 +6391,7 @@
           <t>B | 533呎 (2房)
 $1355万
 $25,417/呎
-(25年-08月-17日)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -6399,7 +6399,7 @@
           <t>C | 819呎 (3房)
 $2866万
 $34,994/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -6407,7 +6407,7 @@
           <t>D | 423呎 (2房)
 $978万
 $23,118/呎
-(25年-04月-10日)</t>
+(25年-04月-11日)</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
@@ -6423,7 +6423,7 @@
           <t>F | 672呎 (3房)
 $1656万
 $24,646/呎
-(25年-07月-17日)</t>
+(25年-07月-18日)</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
           <t>A | 821呎 (3房)
 $1838万
 $22,386/呎
-(25年-07月-09日)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -6446,7 +6446,7 @@
           <t>B | 533呎 (2房)
 $1363万
 $25,578/呎
-(25年-10月-07日)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -6454,7 +6454,7 @@
           <t>C | 819呎 (3房)
 $1860万
 $22,709/呎
-(24年-11月-13日)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -6462,7 +6462,7 @@
           <t>D | 423呎 (2房)
 $940万
 $22,227/呎
-(24年-10月-23日)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -6470,7 +6470,7 @@
           <t>E | 448呎 (2房)
 $1010万
 $22,533/呎
-(24年-11月-17日)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -6478,7 +6478,7 @@
           <t>F | 672呎 (3房)
 $1585万
 $23,591/呎
-(25年-09月-21日)</t>
+(25年-09月-22日)</t>
         </is>
       </c>
     </row>
@@ -6493,7 +6493,7 @@
           <t>A | 821呎 (3房)
 $1768万
 $21,541/呎
-(25年-04月-08日)</t>
+(25年-04月-09日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -6501,7 +6501,7 @@
           <t>B | 533呎 (2房)
 $1279万
 $23,991/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -6509,7 +6509,7 @@
           <t>C | 819呎 (3房)
 $1806万
 $22,048/呎
-(24年-10月-31日)</t>
+(24年-11月-01日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -6517,7 +6517,7 @@
           <t>D | 423呎 (2房)
 $917万
 $21,676/呎
-(24年-12月-09日)</t>
+(24年-12月-10日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -6525,7 +6525,7 @@
           <t>E | 448呎 (2房)
 $980万
 $21,877/呎
-(24年-12月-17日)</t>
+(24年-12月-18日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -6533,7 +6533,7 @@
           <t>F | 672呎 (3房)
 $1539万
 $22,903/呎
-(26年-01月-01日)</t>
+(26年-01月-02日)</t>
         </is>
       </c>
     </row>
@@ -6548,7 +6548,7 @@
           <t>A | 821呎 (3房)
 $1760万
 $21,437/呎
-(25年-11月-23日)</t>
+(25年-11月-24日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -6556,7 +6556,7 @@
           <t>B | 533呎 (2房)
 $1266万
 $23,750/呎
-(25年-03月-26日)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -6564,7 +6564,7 @@
           <t>C | 819呎 (3房)
 $1787万
 $21,823/呎
-(25年-02月-25日)</t>
+(25年-02月-26日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -6572,7 +6572,7 @@
           <t>D | 423呎 (2房)
 $886万
 $20,943/呎
-(24年-11月-06日)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -6580,7 +6580,7 @@
           <t>E | 448呎 (2房)
 $966万
 $21,560/呎
-(24年-12月-22日)</t>
+(24年-12月-23日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -6588,7 +6588,7 @@
           <t>F | 672呎 (3房)
 $1525万
 $22,688/呎
-(26年-01月-28日)</t>
+(26年-01月-29日)</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
           <t>A | 821呎 (3房)
 $1731万
 $21,084/呎
-(25年-12月-14日)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -6611,7 +6611,7 @@
           <t>B | 533呎 (2房)
 $1229万
 $23,060/呎
-(24年-12月-02日)</t>
+(24年-12月-03日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -6619,7 +6619,7 @@
           <t>C | 819呎 (3房)
 $1744万
 $21,298/呎
-(25年-01月-08日)</t>
+(25年-01月-09日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -6627,7 +6627,7 @@
           <t>D | 423呎 (2房)
 $878万
 $20,764/呎
-(24年-12月-02日)</t>
+(24年-12月-03日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -6635,7 +6635,7 @@
           <t>E | 448呎 (2房)
 $938万
 $20,933/呎
-(24年-12月-12日)</t>
+(24年-12月-13日)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -6643,7 +6643,7 @@
           <t>F | 672呎 (3房)
 $1480万
 $22,027/呎
-(26年-02月-10日)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
     </row>
@@ -6658,7 +6658,7 @@
           <t>A | 821呎 (3房)
 $1680万
 $20,458/呎
-(25年-09月-28日)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -6666,7 +6666,7 @@
           <t>B | 533呎 (2房)
 $1188万
 $22,280/呎
-(25年-02月-27日)</t>
+(25年-02月-28日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -6674,7 +6674,7 @@
           <t>C | 819呎 (3房)
 $1685万
 $20,578/呎
-(24年-12月-22日)</t>
+(24年-12月-23日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -6682,7 +6682,7 @@
           <t>D | 423呎 (2房)
 $844万
 $19,965/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -6690,7 +6690,7 @@
           <t>E | 448呎 (2房)
 $906万
 $20,225/呎
-(24年-12月-09日)</t>
+(24年-12月-10日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -6698,7 +6698,7 @@
           <t>F | 672呎 (3房)
 $1430万
 $21,281/呎
-(26年-01月-19日)</t>
+(26年-01月-20日)</t>
         </is>
       </c>
     </row>
@@ -6713,7 +6713,7 @@
           <t>A | 821呎 (3房)
 $1631万
 $19,861/呎
-(25年-01月-23日)</t>
+(25年-01月-24日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -6721,7 +6721,7 @@
           <t>B | 533呎 (2房)
 $1147万
 $21,525/呎
-(24年-12月-17日)</t>
+(24年-12月-18日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -6729,7 +6729,7 @@
           <t>C | 819呎 (3房)
 $1637万
 $19,984/呎
-(24年-11月-19日)</t>
+(24年-11月-20日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -6737,7 +6737,7 @@
           <t>D | 423呎 (2房)
 $820万
 $19,383/呎
-(24年-11月-06日)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -6745,7 +6745,7 @@
           <t>E | 448呎 (2房)
 $902万
 $20,127/呎
-(24年-10月-28日)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -6753,7 +6753,7 @@
           <t>F | 672呎 (3房)
 $1384万
 $20,601/呎
-(25年-12月-01日)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
     </row>
@@ -6768,7 +6768,7 @@
           <t>A | 821呎 (3房)
 $1586万
 $19,322/呎
-(25年-01月-14日)</t>
+(25年-01月-15日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -6776,7 +6776,7 @@
           <t>B | 533呎 (2房)
 $1119万
 $21,000/呎
-(25年-03月-13日)</t>
+(25年-03月-14日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -6784,7 +6784,7 @@
           <t>C | 819呎 (3房)
 $1588万
 $19,389/呎
-(25年-01月-05日)</t>
+(25年-01月-06日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -6792,7 +6792,7 @@
           <t>D | 423呎 (2房)
 $810万
 $19,137/呎
-(24年-11月-06日)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -6800,7 +6800,7 @@
           <t>E | 448呎 (2房)
 $858万
 $19,141/呎
-(24年-10月-23日)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -6808,7 +6808,7 @@
           <t>F | 672呎 (3房)
 $1356万
 $20,176/呎
-(26年-01月-01日)</t>
+(26年-01月-02日)</t>
         </is>
       </c>
     </row>
@@ -6823,7 +6823,7 @@
           <t>A | 821呎 (3房)
 $1568万
 $19,093/呎
-(25年-03月-31日)</t>
+(25年-04月-01日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -6831,7 +6831,7 @@
           <t>B | 533呎 (2房)
 $1092万
 $20,488/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -6839,7 +6839,7 @@
           <t>C | 819呎 (3房)
 $1568万
 $19,140/呎
-(24年-10月-27日)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -6847,7 +6847,7 @@
           <t>D | 423呎 (2房)
 $775万
 $18,319/呎
-(24年-10月-31日)</t>
+(24年-11月-01日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -6855,7 +6855,7 @@
           <t>E | 448呎 (2房)
 $839万
 $18,737/呎
-(24年-10月-28日)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -6863,7 +6863,7 @@
           <t>F | 672呎 (3房)
 $1326万
 $19,735/呎
-(25年-09月-21日)</t>
+(25年-09月-22日)</t>
         </is>
       </c>
     </row>
@@ -6878,7 +6878,7 @@
           <t>A | 821呎 (3房)
 $1550万
 $18,884/呎
-(25年-04月-09日)</t>
+(25年-04月-10日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -6886,7 +6886,7 @@
           <t>B | 533呎 (2房)
 $1065万
 $19,989/呎
-(24年-11月-28日)</t>
+(24年-11月-29日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -6894,7 +6894,7 @@
           <t>C | 819呎 (3房)
 $1551万
 $18,933/呎
-(24年-11月-19日)</t>
+(24年-11月-20日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -6902,7 +6902,7 @@
           <t>D | 423呎 (2房)
 $755万
 $17,839/呎
-(24年-09月-25日)</t>
+(24年-09月-26日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -6910,7 +6910,7 @@
           <t>E | 448呎 (2房)
 $821万
 $18,319/呎
-(24年-11月-28日)</t>
+(24年-11月-29日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -6918,7 +6918,7 @@
           <t>F | 672呎 (3房)
 $1296万
 $19,289/呎
-(24年-12月-23日)</t>
+(24年-12月-24日)</t>
         </is>
       </c>
     </row>
